--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E630B05-FF53-4BCD-B63C-07E3C24E63F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B5ABD8-5BD0-433D-B452-5377F378C8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,10 +92,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>产品募集金额</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>产品成立日期（YYYY-MM-DD)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -145,6 +141,10 @@
   </si>
   <si>
     <t>数据状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>总产品募集金额</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -665,22 +665,22 @@
         <v>17</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>23</v>
       </c>
       <c r="R1" s="10" t="s">
         <v>0</v>
@@ -689,31 +689,31 @@
         <v>1</v>
       </c>
       <c r="T1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="W1" s="13" t="s">
         <v>26</v>
-      </c>
-      <c r="W1" s="13" t="s">
-        <v>27</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="Y1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB1" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="AA1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB1" s="13" t="s">
-        <v>30</v>
       </c>
       <c r="AC1" s="13" t="s">
         <v>4</v>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B5ABD8-5BD0-433D-B452-5377F378C8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9B25E0-288F-40F2-9001-B73D082DBB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
     <t>开放频率</t>
   </si>
   <si>
-    <t>固定持有天数</t>
-  </si>
-  <si>
     <t>产品业绩比较基准</t>
   </si>
   <si>
@@ -145,6 +142,10 @@
   </si>
   <si>
     <t>总产品募集金额</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低持有天数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -248,7 +249,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -280,9 +281,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -632,102 +630,102 @@
   <sheetData>
     <row r="1" spans="1:31" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>22</v>
       </c>
       <c r="R1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="V1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="W1" s="13" t="s">
+      <c r="Y1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y1" s="13" t="s">
+      <c r="Z1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AA1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="13" t="s">
+      <c r="AC1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="13" t="s">
+      <c r="AE1" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="AE1" s="13" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9B25E0-288F-40F2-9001-B73D082DBB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFBD87A-9E58-4092-BF0C-DE865C3BA899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>开放频率</t>
   </si>
@@ -146,6 +146,10 @@
   </si>
   <si>
     <t>最低持有天数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>发行状态</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -596,39 +600,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="18.44140625" customWidth="1"/>
     <col min="3" max="3" width="31.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="29" style="7" customWidth="1"/>
-    <col min="11" max="11" width="27.33203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.77734375" customWidth="1"/>
-    <col min="13" max="13" width="27.109375" style="7" customWidth="1"/>
-    <col min="14" max="14" width="27.33203125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="22.21875" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" customWidth="1"/>
-    <col min="17" max="17" width="19.77734375" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" style="7" customWidth="1"/>
-    <col min="20" max="20" width="17.77734375" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" customWidth="1"/>
-    <col min="22" max="22" width="24" customWidth="1"/>
-    <col min="23" max="23" width="24.33203125" customWidth="1"/>
-    <col min="24" max="24" width="22.109375" customWidth="1"/>
-    <col min="25" max="25" width="17.88671875" customWidth="1"/>
-    <col min="26" max="27" width="22.21875" customWidth="1"/>
-    <col min="28" max="28" width="19.77734375" customWidth="1"/>
-    <col min="29" max="29" width="18.77734375" customWidth="1"/>
-    <col min="30" max="30" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="29" style="7" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="19.77734375" customWidth="1"/>
+    <col min="14" max="14" width="27.109375" style="7" customWidth="1"/>
+    <col min="15" max="15" width="27.33203125" style="7" customWidth="1"/>
+    <col min="16" max="16" width="22.21875" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" customWidth="1"/>
+    <col min="18" max="18" width="19.77734375" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" style="7" customWidth="1"/>
+    <col min="21" max="21" width="17.77734375" customWidth="1"/>
+    <col min="22" max="22" width="22.6640625" customWidth="1"/>
+    <col min="23" max="23" width="24" customWidth="1"/>
+    <col min="24" max="24" width="24.33203125" customWidth="1"/>
+    <col min="25" max="25" width="22.109375" customWidth="1"/>
+    <col min="26" max="26" width="17.88671875" customWidth="1"/>
+    <col min="27" max="28" width="22.21875" customWidth="1"/>
+    <col min="29" max="29" width="19.77734375" customWidth="1"/>
+    <col min="30" max="30" width="18.77734375" customWidth="1"/>
+    <col min="31" max="31" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -642,88 +646,91 @@
         <v>9</v>
       </c>
       <c r="E1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="X1" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="AA1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AB1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AC1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" s="12" t="s">
+      <c r="AD1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="12" t="s">
+      <c r="AE1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AE1" s="12" t="s">
+      <c r="AF1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>2</v>
       </c>
@@ -734,25 +741,25 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:W3" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:X3" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001Export.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFBD87A-9E58-4092-BF0C-DE865C3BA899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,10 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>产品简称</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -150,13 +145,17 @@
   </si>
   <si>
     <t>发行状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -599,40 +598,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="31.125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="16.75" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="29" style="7" customWidth="1"/>
-    <col min="12" max="12" width="27.33203125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="19.77734375" customWidth="1"/>
-    <col min="14" max="14" width="27.109375" style="7" customWidth="1"/>
-    <col min="15" max="15" width="27.33203125" style="7" customWidth="1"/>
-    <col min="16" max="16" width="22.21875" customWidth="1"/>
-    <col min="17" max="17" width="13.33203125" customWidth="1"/>
-    <col min="18" max="18" width="19.77734375" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.6640625" style="7" customWidth="1"/>
-    <col min="21" max="21" width="17.77734375" customWidth="1"/>
-    <col min="22" max="22" width="22.6640625" customWidth="1"/>
+    <col min="12" max="12" width="27.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="19.75" customWidth="1"/>
+    <col min="14" max="14" width="27.125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="27.375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="22.25" customWidth="1"/>
+    <col min="17" max="17" width="13.375" customWidth="1"/>
+    <col min="18" max="18" width="19.75" customWidth="1"/>
+    <col min="19" max="19" width="16.625" customWidth="1"/>
+    <col min="20" max="20" width="16.625" style="7" customWidth="1"/>
+    <col min="21" max="21" width="17.75" customWidth="1"/>
+    <col min="22" max="22" width="22.625" customWidth="1"/>
     <col min="23" max="23" width="24" customWidth="1"/>
-    <col min="24" max="24" width="24.33203125" customWidth="1"/>
-    <col min="25" max="25" width="22.109375" customWidth="1"/>
-    <col min="26" max="26" width="17.88671875" customWidth="1"/>
-    <col min="27" max="28" width="22.21875" customWidth="1"/>
-    <col min="29" max="29" width="19.77734375" customWidth="1"/>
-    <col min="30" max="30" width="18.77734375" customWidth="1"/>
-    <col min="31" max="31" width="17.33203125" customWidth="1"/>
+    <col min="24" max="24" width="24.375" customWidth="1"/>
+    <col min="25" max="25" width="22.125" customWidth="1"/>
+    <col min="26" max="26" width="17.875" customWidth="1"/>
+    <col min="27" max="28" width="22.25" customWidth="1"/>
+    <col min="29" max="29" width="19.75" customWidth="1"/>
+    <col min="30" max="30" width="18.75" customWidth="1"/>
+    <col min="31" max="31" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>6</v>
       </c>
@@ -646,79 +645,79 @@
         <v>9</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>20</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="S1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="X1" s="12" t="s">
         <v>24</v>
-      </c>
-      <c r="X1" s="12" t="s">
-        <v>25</v>
       </c>
       <c r="Y1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="Z1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AB1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="AB1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="AC1" s="12" t="s">
-        <v>28</v>
       </c>
       <c r="AD1" s="12" t="s">
         <v>3</v>
@@ -730,7 +729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.15">
       <c r="D9" t="s">
         <v>2</v>
       </c>
@@ -738,28 +737,28 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S3">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:X3" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:X3">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -769,113 +768,113 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="2"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -885,9 +884,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
